--- a/vscode-sales-report-extension/cleaned_data_20260618.xlsx
+++ b/vscode-sales-report-extension/cleaned_data_20260618.xlsx
@@ -8,9 +8,12 @@
   </bookViews>
   <sheets>
     <sheet name="overview" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="category" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="products" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="traffic" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="funnel" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="category" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="products" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="traffic" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="trend" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="insights" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,10 +22,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
-    <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
-  </numFmts>
+  <numFmts count="0"/>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -61,12 +61,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -432,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:I2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,91 +447,69 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>payment_amount</t>
+          <t>refund_amount</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>refund_amount</t>
+          <t>orders</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>orders</t>
+          <t>pay_users</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>pay_users</t>
+          <t>visitors</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>visitors</t>
+          <t>aov</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>refund_rate</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
           <t>pay_cvr</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>aov</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>refund_rate</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>add_to_cart</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>favorites</t>
-        </is>
-      </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="n">
-        <v>46191</v>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
       </c>
       <c r="B2" t="n">
-        <v>102675.2</v>
+        <v>91390.59999999999</v>
       </c>
       <c r="C2" t="n">
-        <v>102675.2</v>
+        <v>37353.1</v>
       </c>
       <c r="D2" t="n">
-        <v>26068.5</v>
+        <v>24</v>
       </c>
       <c r="E2" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="F2" t="n">
-        <v>26</v>
+        <v>2538</v>
       </c>
       <c r="G2" t="n">
-        <v>26</v>
+        <v>3807.94</v>
       </c>
       <c r="H2" t="n">
-        <v>3949.0462</v>
+        <v>0.2901</v>
       </c>
       <c r="I2" t="n">
-        <v>3949.05</v>
-      </c>
-      <c r="J2" t="n">
-        <v>0.2025</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L2" t="n">
-        <v>0</v>
+        <v>0.0122</v>
       </c>
     </row>
   </sheetData>
@@ -546,189 +523,91 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L4"/>
+  <dimension ref="A1:J2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>visitors</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>sales_amount</t>
+          <t>order_placers</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>qty</t>
+          <t>payers</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>orders</t>
+          <t>success_buyers</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>pay_users</t>
+          <t>order_rate</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>visitors</t>
+          <t>pay_rate</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>cvr</t>
+          <t>success_rate</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>refund_rate</t>
+          <t>full_cvr</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>favorites</t>
+          <t>inquiry_count</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>cart_add</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>new_user_rate</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>repeat_user_rate</t>
+          <t>inquiry_rate</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>嵌入式冰箱</t>
-        </is>
+      <c r="A2" t="n">
+        <v>2538</v>
       </c>
       <c r="B2" t="n">
-        <v>86379.3</v>
+        <v>48</v>
       </c>
       <c r="C2" t="n">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="D2" t="n">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="E2" t="n">
-        <v>18</v>
+        <v>0.0189</v>
       </c>
       <c r="F2" t="n">
-        <v>18</v>
+        <v>0.6458</v>
       </c>
       <c r="G2" t="n">
         <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>0.0122</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>洗碗机</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>11602</v>
-      </c>
-      <c r="C3" t="n">
-        <v>7</v>
-      </c>
-      <c r="D3" t="n">
-        <v>7</v>
-      </c>
-      <c r="E3" t="n">
-        <v>7</v>
-      </c>
-      <c r="F3" t="n">
-        <v>7</v>
-      </c>
-      <c r="G3" t="n">
-        <v>1</v>
-      </c>
-      <c r="H3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L3" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>厨房冰箱</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>4693.9</v>
-      </c>
-      <c r="C4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>1</v>
+        <v>0.212</v>
       </c>
     </row>
   </sheetData>
@@ -742,13 +621,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M10"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>product_name</t>
+          <t>category</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -768,452 +647,106 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>refund_amount</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>refund_rate</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>sales_share</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>pay_users</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>visitors</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>sku</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>cvr</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>refund_rate</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>favorites</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>cart_add</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>new_user_rate</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>repeat_user_rate</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>松下(Panasonic)冰箱Xtra黑布林500升十字一级家用自动制冰大容量</t>
+          <t>嵌入式冰箱</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>32396.9</v>
+        <v>75094.7</v>
       </c>
       <c r="C2" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="D2" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="E2" t="n">
-        <v>8</v>
+        <v>37353.1</v>
       </c>
       <c r="F2" t="n">
-        <v>8</v>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>0.3322</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.8217</v>
       </c>
       <c r="H2" t="n">
-        <v>1</v>
-      </c>
-      <c r="I2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M2" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>松下(Panasonic)冰箱白月光五门515L超薄零嵌入法式无霜自动制冰</t>
+          <t>洗碗机</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>18279.25</v>
+        <v>11602</v>
       </c>
       <c r="C3" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D3" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>3</v>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.1269</v>
       </c>
       <c r="H3" t="n">
-        <v>1</v>
-      </c>
-      <c r="I3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M3" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>松下(Panasonic)小法棍Pro风冷415升多门法式冰箱NR-XG42GEA-W</t>
+          <t>厨房冰箱</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>14928.3</v>
+        <v>4693.9</v>
       </c>
       <c r="C4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>3</v>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.0514</v>
       </c>
       <c r="H4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M4" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>松下白月光3.0十字冰箱家用零嵌入自动制冰新一级能效ED51APB-W</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>12598</v>
-      </c>
-      <c r="C5" t="n">
-        <v>2</v>
-      </c>
-      <c r="D5" t="n">
-        <v>2</v>
-      </c>
-      <c r="E5" t="n">
-        <v>2</v>
-      </c>
-      <c r="F5" t="n">
-        <v>2</v>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>松下洗碗机台式80℃高温除菌独立烘干家用刷碗机NP-UW5HH1D</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>9736</v>
-      </c>
-      <c r="C6" t="n">
-        <v>6</v>
-      </c>
-      <c r="D6" t="n">
-        <v>6</v>
-      </c>
-      <c r="E6" t="n">
-        <v>6</v>
-      </c>
-      <c r="F6" t="n">
-        <v>6</v>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>松下白月光冰箱510L大容量超薄零嵌入十字家用冰箱NR-ED51CSA-W</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>5389.85</v>
-      </c>
-      <c r="C7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D7" t="n">
-        <v>1</v>
-      </c>
-      <c r="E7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H7" t="n">
-        <v>1</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>松下(Panasonic)冰箱大白鲸505L超薄大容量嵌入式对开门一级能效</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>4693.9</v>
-      </c>
-      <c r="C8" t="n">
-        <v>1</v>
-      </c>
-      <c r="D8" t="n">
-        <v>1</v>
-      </c>
-      <c r="E8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F8" t="n">
-        <v>1</v>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H8" t="n">
-        <v>1</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>松下(Panasonic)冰箱三门300升一级能效自动制冰风冷无霜电冰箱</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>2787</v>
-      </c>
-      <c r="C9" t="n">
-        <v>1</v>
-      </c>
-      <c r="D9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E9" t="n">
-        <v>1</v>
-      </c>
-      <c r="F9" t="n">
-        <v>1</v>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H9" t="n">
-        <v>1</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>松下洗碗机台式5套家用自动智能刷碗机高温除菌小型台面式K8RAH5D</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>1866</v>
-      </c>
-      <c r="C10" t="n">
-        <v>1</v>
-      </c>
-      <c r="D10" t="n">
-        <v>1</v>
-      </c>
-      <c r="E10" t="n">
-        <v>1</v>
-      </c>
-      <c r="F10" t="n">
-        <v>1</v>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H10" t="n">
-        <v>1</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1228,129 +761,1256 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:I9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>source</t>
+          <t>product_name</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>value</t>
+          <t>sku</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>sales_amount</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>qty</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>orders</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>pay_users</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>avg_price</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>refund_amount</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>refund_rate</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>****</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>6</v>
+          <t>松下(Panasonic)冰箱Xtra黑布林500升十字一级家用自动制冰大容量</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>785913456976</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>32396.9</v>
+      </c>
+      <c r="D2" t="n">
+        <v>8</v>
+      </c>
+      <c r="E2" t="n">
+        <v>8</v>
+      </c>
+      <c r="F2" t="n">
+        <v>8</v>
+      </c>
+      <c r="G2" t="n">
+        <v>4049</v>
+      </c>
+      <c r="H2" t="n">
+        <v>8192.299999999999</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.2018</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>广东省</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>5</v>
+          <t>松下(Panasonic)小法棍Pro风冷415升多门法式冰箱NR-XG42GEA-W</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>927954652878</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>14928.3</v>
+      </c>
+      <c r="D3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F3" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3" t="n">
+        <v>4976</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>湖北省</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>3</v>
+          <t>松下白月光3.0十字冰箱家用零嵌入自动制冰新一级能效ED51APB-W</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>964415016796</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>12598</v>
+      </c>
+      <c r="D4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F4" t="n">
+        <v>2</v>
+      </c>
+      <c r="G4" t="n">
+        <v>6299</v>
+      </c>
+      <c r="H4" t="n">
+        <v>6499</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.3403</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>福建省</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>3</v>
+          <t>松下(Panasonic)冰箱白月光五门515L超薄零嵌入法式无霜自动制冰</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>927407420693</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>12384.5</v>
+      </c>
+      <c r="D5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G5" t="n">
+        <v>6192</v>
+      </c>
+      <c r="H5" t="n">
+        <v>5894.75</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.3225</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>安徽省</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>2</v>
+          <t>松下洗碗机台式80℃高温除菌独立烘干家用刷碗机NP-UW5HH1D</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>964028962671</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>9736</v>
+      </c>
+      <c r="D6" t="n">
+        <v>6</v>
+      </c>
+      <c r="E6" t="n">
+        <v>6</v>
+      </c>
+      <c r="F6" t="n">
+        <v>6</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1622</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>江苏省</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>2</v>
+          <t>松下(Panasonic)冰箱大白鲸505L超薄大容量嵌入式对开门一级能效</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>785464678484</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>4693.9</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" t="n">
+        <v>4693</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>上海市</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
+          <t>松下(Panasonic)冰箱三门300升一级能效自动制冰风冷无霜电冰箱</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>785476454188</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>2787</v>
+      </c>
+      <c r="D8" t="n">
         <v>1</v>
+      </c>
+      <c r="E8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" t="n">
+        <v>2787</v>
+      </c>
+      <c r="H8" t="n">
+        <v>5774</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.6745</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>吉林省</t>
+          <t>松下洗碗机台式5套家用自动智能刷碗机高温除菌小型台面式K8RAH5D</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>964400683695</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>1866</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1866</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>sales</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>其他(数据脱敏)</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>18</v>
+      </c>
+      <c r="C2" t="n">
+        <v>70005.55</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>广东省</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3" t="n">
+        <v>6908.65</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>上海市</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" t="n">
+        <v>1546</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>安徽省</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" t="n">
+        <v>4104.65</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>江苏省</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" t="n">
+        <v>4976.1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>福建省</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" t="n">
+        <v>3849.65</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>days</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>sales</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>visitors</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>orders</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>cvr</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>88854.05</v>
+      </c>
+      <c r="C2" t="n">
+        <v>752</v>
+      </c>
+      <c r="D2" t="n">
+        <v>19</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.0252659574468085</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>46036.05</v>
+      </c>
+      <c r="C3" t="n">
+        <v>1084</v>
+      </c>
+      <c r="D3" t="n">
+        <v>9</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.00830258302583026</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>21602.15</v>
+      </c>
+      <c r="C4" t="n">
+        <v>1036</v>
+      </c>
+      <c r="D4" t="n">
+        <v>6</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.00579150579150579</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>19965.45</v>
+      </c>
+      <c r="C5" t="n">
+        <v>904</v>
+      </c>
+      <c r="D5" t="n">
+        <v>6</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.00553097345132743</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>27785.6</v>
+      </c>
+      <c r="C6" t="n">
+        <v>771</v>
+      </c>
+      <c r="D6" t="n">
+        <v>8</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.0103761348897536</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>34330.6</v>
+      </c>
+      <c r="C7" t="n">
+        <v>839</v>
+      </c>
+      <c r="D7" t="n">
+        <v>9</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.0107270560190703</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>26927.7</v>
+      </c>
+      <c r="C8" t="n">
+        <v>850</v>
+      </c>
+      <c r="D8" t="n">
+        <v>8</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.00941176470588235</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1</v>
+        <v>37034.7</v>
+      </c>
+      <c r="C9" t="n">
+        <v>1730</v>
+      </c>
+      <c r="D9" t="n">
+        <v>10</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.00578034682080925</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>浙江省</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1</v>
+        <v>45682.45</v>
+      </c>
+      <c r="C10" t="n">
+        <v>2283</v>
+      </c>
+      <c r="D10" t="n">
+        <v>12</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.00525624178712221</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>辽宁省</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1</v>
+        <v>79447.05</v>
+      </c>
+      <c r="C11" t="n">
+        <v>2380</v>
+      </c>
+      <c r="D11" t="n">
+        <v>21</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.008823529411764709</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>陕西省</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1</v>
+        <v>66206.45</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1869</v>
+      </c>
+      <c r="D12" t="n">
+        <v>20</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.0101658640984484</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>35774.7</v>
+      </c>
+      <c r="C13" t="n">
+        <v>1936</v>
+      </c>
+      <c r="D13" t="n">
+        <v>12</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.00619834710743802</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>102075.95</v>
+      </c>
+      <c r="C14" t="n">
+        <v>1910</v>
+      </c>
+      <c r="D14" t="n">
+        <v>20</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.009947643979057589</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>86730.21000000001</v>
+      </c>
+      <c r="C15" t="n">
+        <v>1769</v>
+      </c>
+      <c r="D15" t="n">
+        <v>16</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.00847936687394008</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>62638</v>
+      </c>
+      <c r="C16" t="n">
+        <v>1467</v>
+      </c>
+      <c r="D16" t="n">
+        <v>17</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.010906612133606</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>61867.7</v>
+      </c>
+      <c r="C17" t="n">
+        <v>1462</v>
+      </c>
+      <c r="D17" t="n">
+        <v>16</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.0109439124487004</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>42007.85</v>
+      </c>
+      <c r="C18" t="n">
+        <v>1386</v>
+      </c>
+      <c r="D18" t="n">
+        <v>10</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.00649350649350649</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>41443.65</v>
+      </c>
+      <c r="C19" t="n">
+        <v>1586</v>
+      </c>
+      <c r="D19" t="n">
+        <v>10</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.00630517023959647</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>26901.45</v>
+      </c>
+      <c r="C20" t="n">
+        <v>1759</v>
+      </c>
+      <c r="D20" t="n">
+        <v>7</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.00397953382603752</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>47828.45</v>
+      </c>
+      <c r="C21" t="n">
+        <v>1663</v>
+      </c>
+      <c r="D21" t="n">
+        <v>14</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.007817197835237519</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>130928.65</v>
+      </c>
+      <c r="C22" t="n">
+        <v>1493</v>
+      </c>
+      <c r="D22" t="n">
+        <v>21</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0.0120562625586068</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>198513.05</v>
+      </c>
+      <c r="C23" t="n">
+        <v>1686</v>
+      </c>
+      <c r="D23" t="n">
+        <v>16</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0.00652431791221827</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>61597</v>
+      </c>
+      <c r="C24" t="n">
+        <v>1828</v>
+      </c>
+      <c r="D24" t="n">
+        <v>20</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.0103938730853392</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>89936.89999999999</v>
+      </c>
+      <c r="C25" t="n">
+        <v>2063</v>
+      </c>
+      <c r="D25" t="n">
+        <v>28</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.0111488124091129</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>75779.75</v>
+      </c>
+      <c r="C26" t="n">
+        <v>2388</v>
+      </c>
+      <c r="D26" t="n">
+        <v>20</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.007956448911222779</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>58462.8</v>
+      </c>
+      <c r="C27" t="n">
+        <v>2082</v>
+      </c>
+      <c r="D27" t="n">
+        <v>14</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.00624399615754083</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>136890.65</v>
+      </c>
+      <c r="C28" t="n">
+        <v>2261</v>
+      </c>
+      <c r="D28" t="n">
+        <v>31</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.0119416187527643</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>145729.4</v>
+      </c>
+      <c r="C29" t="n">
+        <v>2380</v>
+      </c>
+      <c r="D29" t="n">
+        <v>39</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.0126050420168067</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>130444.9</v>
+      </c>
+      <c r="C30" t="n">
+        <v>2627</v>
+      </c>
+      <c r="D30" t="n">
+        <v>37</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.0129425199847735</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>133883.7</v>
+      </c>
+      <c r="C31" t="n">
+        <v>2538</v>
+      </c>
+      <c r="D31" t="n">
+        <v>32</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.012214342001576</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>level</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>yellow</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>全店转化率有提升空间</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>全店转化率 1.22%（访客→成团），距行业均值仍有差距。下单率 1.89%，建议通过评价优化、限时促销、主图A/B测试提升转化。</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>yellow</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>下单→支付有优化空间</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>支付率 64.58%，仍有 17 人下单后放弃。建议在结算页增加信任标识（7天无理由/正品保证），减少支付摩擦。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>客服询单转化分析</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>当日询单 85 人，询单转化率 21.2%。高客单价家电品类客服介入对转化至关重要，建议加强客服专业培训与响应速度。</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>退款率严重偏高</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>退款率高达 29.0%（退款¥37,353/成团¥91,391），远超家电行业正常水平(1-5%)。需紧急排查：①商品质量/描述不符 ②物流破损 ③售后处理周期。建议逐单分析退款原因并建立预警机制。</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>高客单价优势明显</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>客单价 ¥3,808，属于高客单家电品类。建议：①推出分期免息服务降低决策门槛 ②强化延保/安装等增值服务提升ARPU ③用内容营销（评测/安装案例）增强信任。</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>yellow</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>品类集中度偏高</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>"嵌入式冰箱"占销售额82%，依赖度过高存在风险。建议培育第二增长品类，分散单品/品类波动风险。</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>高风险品类预警</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>"嵌入式冰箱"退款率偏高，建议重点排查该品类商品质量、详情页描述准确性和物流包装。</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>流量效率分析</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>单访客价值 ¥36.01（成团金额/访客数）。参考标准：冰箱品类单访客价值通常在¥3-8。当前高于均值，建议维持高意向流量获取策略。</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>近7日销售额上升趋势</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>近7日均销 ¥110,161，较前7日增长40%。趋势向好，建议维持当前运营节奏并观察可持续性。</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>TOP1商品: 松下(Panasonic)冰箱Xtra黑布林500</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>销售额 ¥32,397（8件），占总销售35%。退款率偏高，需关注售后。</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>P0/P1 行动建议</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>①【紧急】逐单分析退款原因，建立退款分类标签（质量/物流/描述/其他）；②【重点】优化商详页主图视频+核心卖点首屏展示，提升访客→下单率；③【重要】配置下单未支付自动催付机制（优惠券/短信提醒）；④【常规】关注竞品618后价格策略，合理调整促销力度；⑤【常规】高客单客户建联与私域沉淀，推动复购与口碑转介绍</t>
+        </is>
       </c>
     </row>
   </sheetData>
